--- a/MRM-CalQc/report/小靶标/FFA/others/FFA-Targeted Analyte Information.xlsx
+++ b/MRM-CalQc/report/小靶标/FFA/others/FFA-Targeted Analyte Information.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18480" windowHeight="11640"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -17,22 +17,28 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="313">
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>序号</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>化合物名称</t>
     </r>
@@ -42,11 +48,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>缩写</t>
     </r>
@@ -56,33 +65,42 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>分子式</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>分子量</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>分类</t>
     </r>
@@ -95,29 +113,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-9-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十八碳烯酸（油酸）</t>
     </r>
@@ -145,11 +166,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十六烷酸（棕榈酸）</t>
     </r>
@@ -174,11 +198,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>辛酸</t>
     </r>
@@ -203,11 +230,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>癸酸</t>
     </r>
@@ -232,29 +262,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>反式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-9-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十八碳烯酸（反油酸）</t>
     </r>
@@ -270,11 +303,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十二烷酸（月桂酸）</t>
     </r>
@@ -299,29 +335,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-9,12-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>亚油酸</t>
     </r>
@@ -349,11 +388,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>肉豆蔻酸</t>
     </r>
@@ -378,11 +420,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十五烷酸</t>
     </r>
@@ -407,11 +452,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十八烷酸（硬脂酸）</t>
     </r>
@@ -436,11 +484,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十三烷酸</t>
     </r>
@@ -465,11 +516,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十二烷酸（山嵛酸）</t>
     </r>
@@ -494,11 +548,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十一烷酸</t>
     </r>
@@ -523,11 +580,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>花生四烯酸</t>
     </r>
@@ -552,11 +612,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十三烷酸</t>
     </r>
@@ -578,20 +641,23 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>α-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>亚麻酸</t>
     </r>
@@ -619,29 +685,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-4,7,10,13,16-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十二碳五烯酸</t>
     </r>
@@ -663,29 +732,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-5,8,11,14,17-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十碳五烯酸</t>
     </r>
@@ -710,29 +782,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-9-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>肉豆蔻油酸</t>
     </r>
@@ -741,7 +816,7 @@
     <t>Myristoleic acid</t>
   </si>
   <si>
-    <t>C14:1 </t>
+    <t xml:space="preserve">C14:1 </t>
   </si>
   <si>
     <t>544-64-9</t>
@@ -760,11 +835,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十四烷酸（木蜡酸）</t>
     </r>
@@ -789,29 +867,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-13-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>芥酸</t>
     </r>
@@ -836,29 +917,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-6-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十八碳烯酸</t>
     </r>
@@ -877,29 +961,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-4,7,10,13,16,19-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十二碳六烯酸</t>
     </r>
@@ -924,11 +1011,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十烷酸（花生酸）</t>
     </r>
@@ -953,29 +1043,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-7,10,13,16-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十二碳四烯酸</t>
     </r>
@@ -1000,29 +1093,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-11-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十碳烯酸</t>
     </r>
@@ -1047,11 +1143,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十七烷酸</t>
     </r>
@@ -1073,11 +1172,14 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十一烷酸</t>
     </r>
@@ -1099,29 +1201,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-15-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>神经酸</t>
     </r>
@@ -1145,821 +1250,852 @@
     <t>C08323</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+    <t>顺式-8, 11, 14-二十碳三烯酸</t>
+  </si>
+  <si>
+    <t>all-cis-8, 11, 14-Eicosatrienoic Acid</t>
+  </si>
+  <si>
+    <t>C20:3/DGLA</t>
+  </si>
+  <si>
+    <t>1783-84-2</t>
+  </si>
+  <si>
+    <t>C20H34O2</t>
+  </si>
+  <si>
+    <t>HMDB0002925</t>
+  </si>
+  <si>
+    <t>C03242</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>γ-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>亚麻酸</t>
+    </r>
+  </si>
+  <si>
+    <t>gamma-Linolenic acid</t>
+  </si>
+  <si>
+    <t>C18:3</t>
+  </si>
+  <si>
+    <t>506-26-3</t>
+  </si>
+  <si>
+    <t>HMDB0003073</t>
+  </si>
+  <si>
+    <t>C06426</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-8,11,14-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>亚麻酸</t>
-    </r>
-  </si>
-  <si>
-    <t>cis,cis,cis-8,11,14-Linolenic Acid</t>
-  </si>
-  <si>
-    <t>C20:3/DGLA</t>
-  </si>
-  <si>
-    <t>1783-84-2</t>
-  </si>
-  <si>
-    <t>C20H34O2</t>
-  </si>
-  <si>
-    <t>HMDB0002925</t>
-  </si>
-  <si>
-    <t>C03242</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <family val="2"/>
+      </rPr>
+      <t>-9-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>棕榈油酸</t>
+    </r>
+  </si>
+  <si>
+    <t>Palmitoleic acid</t>
+  </si>
+  <si>
+    <t>C16:1</t>
+  </si>
+  <si>
+    <t>373-49-9</t>
+  </si>
+  <si>
+    <t>C16H30O2</t>
+  </si>
+  <si>
+    <t>n-7</t>
+  </si>
+  <si>
+    <t>HMDB0003229</t>
+  </si>
+  <si>
+    <t>C08362</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>反式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>γ-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>亚麻酸</t>
-    </r>
-  </si>
-  <si>
-    <t>gamma-Linolenic acid</t>
-  </si>
-  <si>
-    <t>C18:3</t>
-  </si>
-  <si>
-    <t>506-26-3</t>
-  </si>
-  <si>
-    <t>HMDB0003073</t>
-  </si>
-  <si>
-    <t>C06426</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <family val="2"/>
+      </rPr>
+      <t>-11-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>十八碳烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>trans-11-Octadecenoic acid</t>
+  </si>
+  <si>
+    <t>693-72-1</t>
+  </si>
+  <si>
+    <t>HMDB0003231</t>
+  </si>
+  <si>
+    <t>C08367</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
+      </rPr>
+      <t>-11,14-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>二十碳二烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>cis,cis-11,14-Eicosadienoic Acid</t>
+  </si>
+  <si>
+    <t>C20:2</t>
+  </si>
+  <si>
+    <t>5598-38-9</t>
+  </si>
+  <si>
+    <t>C20H36O2</t>
+  </si>
+  <si>
+    <t>HMDB0005060</t>
+  </si>
+  <si>
+    <t>C16525</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>反式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>-9,12-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>亚油酸</t>
+    </r>
+  </si>
+  <si>
+    <t>Linoelaidic acid</t>
+  </si>
+  <si>
+    <t>C18:2</t>
+  </si>
+  <si>
+    <t>506-21-8</t>
+  </si>
+  <si>
+    <t>HMDB0006270</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>顺式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>-7,10,13,16,19-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>二十二碳五烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>all-cis-7,10,13,16,19-Docosapentaenoic acid</t>
+  </si>
+  <si>
+    <t>C22:5/DPA</t>
+  </si>
+  <si>
+    <t>24880-45-3</t>
+  </si>
+  <si>
+    <t>HMDB0006528</t>
+  </si>
+  <si>
+    <t>C16513</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>反式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
       </rPr>
       <t>-9-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>棕榈油酸</t>
     </r>
   </si>
   <si>
-    <t>Palmitoleic acid</t>
-  </si>
-  <si>
-    <t>C16:1</t>
-  </si>
-  <si>
-    <t>373-49-9</t>
-  </si>
-  <si>
-    <t>C16H30O2</t>
-  </si>
-  <si>
-    <t>n-7</t>
-  </si>
-  <si>
-    <t>HMDB0003229</t>
-  </si>
-  <si>
-    <t>C08362</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+    <t>Palmitelaidic acid</t>
+  </si>
+  <si>
+    <t>10030-74-7</t>
+  </si>
+  <si>
+    <t>HMDB0012328</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>顺式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>-10-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>十七碳烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>cis-10-Heptadecenoic Acid</t>
+  </si>
+  <si>
+    <t>C17:1</t>
+  </si>
+  <si>
+    <t>29743-97-3</t>
+  </si>
+  <si>
+    <t>C17H32O2</t>
+  </si>
+  <si>
+    <t>HMDB0060038</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>顺式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>-11,14,17-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>二十碳三烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>all-cis-11,14,17-Eicosatrienoic Acid</t>
+  </si>
+  <si>
+    <t>C20:3/ETE</t>
+  </si>
+  <si>
+    <t>17046-59-2</t>
+  </si>
+  <si>
+    <t>HMDB0060039</t>
+  </si>
+  <si>
+    <t>C16522</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>顺式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>-13,16-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>二十二碳二烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>cis,cis-13,16-Docosadienoic Acid</t>
+  </si>
+  <si>
+    <t>C22:2</t>
+  </si>
+  <si>
+    <t>17735-98-7</t>
+  </si>
+  <si>
+    <t>C22H40O2</t>
+  </si>
+  <si>
+    <t>HMDB0061714</t>
+  </si>
+  <si>
+    <t>C16533</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>反式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
+      </rPr>
+      <t>-9-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>肉豆蔻油酸</t>
+    </r>
+  </si>
+  <si>
+    <t>Myristelaidic acid</t>
+  </si>
+  <si>
+    <t>50286-30-1</t>
+  </si>
+  <si>
+    <t>HMDB0062248</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>顺式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
       </rPr>
       <t>-11-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>十八碳烯酸</t>
     </r>
   </si>
   <si>
-    <t>trans-11-Octadecenoic acid</t>
-  </si>
-  <si>
-    <t>693-72-1</t>
-  </si>
-  <si>
-    <t>HMDB0003231</t>
-  </si>
-  <si>
-    <t>C08367</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+    <t>cis-11-Octadecenoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">506-17-2 </t>
+  </si>
+  <si>
+    <t>HMDB0240219</t>
+  </si>
+  <si>
+    <t>C21944</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>反式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>-10-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>十七碳烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>trans-10-Heptadecenoic acid</t>
+  </si>
+  <si>
+    <t>126761-43-1</t>
+  </si>
+  <si>
+    <t>HMDB0244268</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>反式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>-13-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>二十二碳烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>trans-13-Docosenoic acid</t>
+  </si>
+  <si>
+    <t>506-33-2</t>
+  </si>
+  <si>
+    <t>HMDB0249369</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>反式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>-6-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>十八碳烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>6-Octadecenoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">593-40-8 </t>
+  </si>
+  <si>
+    <t>HMDB0303337</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>顺式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-11,14-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>二十碳二烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>cis,cis-11,14-Eicosadienoic Acid</t>
-  </si>
-  <si>
-    <t>C20:2</t>
-  </si>
-  <si>
-    <t>5598-38-9</t>
-  </si>
-  <si>
-    <t>C20H36O2</t>
-  </si>
-  <si>
-    <t>HMDB0005060</t>
-  </si>
-  <si>
-    <t>C16525</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <family val="2"/>
+      </rPr>
+      <t>-10-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>十五碳烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>cis-10-Pentadecenoic Acid</t>
+  </si>
+  <si>
+    <t>C15:1</t>
+  </si>
+  <si>
+    <t>84743-29-3</t>
+  </si>
+  <si>
+    <t>C15H28O2</t>
+  </si>
+  <si>
+    <t>HMDB0304816</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>反式</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-9,12-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>亚油酸</t>
-    </r>
-  </si>
-  <si>
-    <t>Linoelaidic acid</t>
-  </si>
-  <si>
-    <t>C18:2</t>
-  </si>
-  <si>
-    <t>506-21-8</t>
-  </si>
-  <si>
-    <t>HMDB0006270</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顺式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <family val="2"/>
+      </rPr>
+      <t>-10-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>十五碳烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>trans-10-pentadecenoic acid</t>
+  </si>
+  <si>
+    <t>321744-58-5</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>反式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-7,10,13,16,19-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>二十二碳五烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>all-cis-7,10,13,16,19-Docosapentaenoic acid</t>
-  </si>
-  <si>
-    <t>C22:5/DPA</t>
-  </si>
-  <si>
-    <t>24880-45-3</t>
-  </si>
-  <si>
-    <t>HMDB0006528</t>
-  </si>
-  <si>
-    <t>C16513</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>十九碳烯酸</t>
+    </r>
+  </si>
+  <si>
+    <t>trans-10-Nonadecenoic acid</t>
+  </si>
+  <si>
+    <t>C19:1</t>
+  </si>
+  <si>
+    <t>67228-95-9</t>
+  </si>
+  <si>
+    <t>C19H36O2</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>反</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-9-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>棕榈油酸</t>
-    </r>
-  </si>
-  <si>
-    <t>Palmitelaidic acid</t>
-  </si>
-  <si>
-    <t>10030-74-7</t>
-  </si>
-  <si>
-    <t>HMDB0012328</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顺式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-10-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>十七碳烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>cis-10-Heptadecenoic Acid</t>
-  </si>
-  <si>
-    <t>C17:1</t>
-  </si>
-  <si>
-    <t>29743-97-3</t>
-  </si>
-  <si>
-    <t>C17H32O2</t>
-  </si>
-  <si>
-    <t>HMDB0060038</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顺式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-11,14,17-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>二十碳三烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>all-cis-11,14,17-Eicosatrienoic Acid</t>
-  </si>
-  <si>
-    <t>C20:3/ETE</t>
-  </si>
-  <si>
-    <t>17046-59-2</t>
-  </si>
-  <si>
-    <t>HMDB0060039</t>
-  </si>
-  <si>
-    <t>C16522</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顺式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-13,16-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>二十二碳二烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>cis,cis-13,16-Docosadienoic Acid</t>
-  </si>
-  <si>
-    <t>C22:2</t>
-  </si>
-  <si>
-    <t>17735-98-7</t>
-  </si>
-  <si>
-    <t>C22H40O2</t>
-  </si>
-  <si>
-    <t>HMDB0061714</t>
-  </si>
-  <si>
-    <t>C16533</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-9-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>肉豆蔻油酸</t>
-    </r>
-  </si>
-  <si>
-    <t>Myristelaidic acid</t>
-  </si>
-  <si>
-    <t>50286-30-1</t>
-  </si>
-  <si>
-    <t>HMDB0062248</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顺式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-11-</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>十八碳烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>cis-11-Octadecenoic acid</t>
-  </si>
-  <si>
-    <t>506-17-2 </t>
-  </si>
-  <si>
-    <t>HMDB0240219</t>
-  </si>
-  <si>
-    <t>C21944</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-10-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>十七碳烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>trans-10-Heptadecenoic acid</t>
-  </si>
-  <si>
-    <t>126761-43-1</t>
-  </si>
-  <si>
-    <t>HMDB0244268</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-13-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>二十二碳烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>trans-13-Docosenoic acid</t>
-  </si>
-  <si>
-    <t>506-33-2</t>
-  </si>
-  <si>
-    <t>HMDB0249369</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-6-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>十八碳烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>6-Octadecenoic acid</t>
-  </si>
-  <si>
-    <t>593-40-8 </t>
-  </si>
-  <si>
-    <t>HMDB0303337</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顺式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-10-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>十五碳烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>cis-10-Pentadecenoic Acid</t>
-  </si>
-  <si>
-    <t>C15:1</t>
-  </si>
-  <si>
-    <t>84743-29-3</t>
-  </si>
-  <si>
-    <t>C15H28O2</t>
-  </si>
-  <si>
-    <t>HMDB0304816</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-10-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>十五碳烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>trans-10-pentadecenoic acid</t>
-  </si>
-  <si>
-    <t>321744-58-5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>十九碳烯酸</t>
-    </r>
-  </si>
-  <si>
-    <t>trans-10-Nonadecenoic acid</t>
-  </si>
-  <si>
-    <t>C19:1</t>
-  </si>
-  <si>
-    <t>67228-95-9</t>
-  </si>
-  <si>
-    <t>C19H36O2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-11-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
       </rPr>
       <t>二十碳烯酸</t>
     </r>
@@ -1974,373 +2110,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2350,46 +2151,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2397,300 +2168,68 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="11">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -2717,82 +2256,82 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2804,159 +2343,193 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:N50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="38.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="49.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.375" style="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="38.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="49.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="11.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="11.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="9.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="5.147857142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="8.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="8" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="8" width="38.14785714285715" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -2974,7 +2547,7 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -2986,9 +2559,13 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2">
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -3006,7 +2583,7 @@
       <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>282.4614</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -3018,9 +2595,13 @@
       <c r="J2" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2">
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -3038,7 +2619,7 @@
       <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3">
         <v>256.4241</v>
       </c>
       <c r="H3" s="2"/>
@@ -3048,9 +2629,13 @@
       <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2">
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -3068,7 +2653,7 @@
       <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>144.21</v>
       </c>
       <c r="H4" s="2"/>
@@ -3078,9 +2663,13 @@
       <c r="J4" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2">
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -3098,7 +2687,7 @@
       <c r="F5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>172.26</v>
       </c>
       <c r="H5" s="2"/>
@@ -3108,9 +2697,13 @@
       <c r="J5" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -3128,7 +2721,7 @@
       <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>282.4614</v>
       </c>
       <c r="H6" s="2"/>
@@ -3136,9 +2729,13 @@
         <v>42</v>
       </c>
       <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2">
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -3156,7 +2753,7 @@
       <c r="F7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="3">
         <v>200.32</v>
       </c>
       <c r="H7" s="2"/>
@@ -3166,9 +2763,13 @@
       <c r="J7" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2">
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -3186,7 +2787,7 @@
       <c r="F8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="3">
         <v>280.4455</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -3198,9 +2799,13 @@
       <c r="J8" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2">
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -3218,7 +2823,7 @@
       <c r="F9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <v>228.37</v>
       </c>
       <c r="H9" s="2"/>
@@ -3228,9 +2833,13 @@
       <c r="J9" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2">
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -3248,7 +2857,7 @@
       <c r="F10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="3">
         <v>242.4</v>
       </c>
       <c r="H10" s="2"/>
@@ -3258,9 +2867,13 @@
       <c r="J10" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2">
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -3278,7 +2891,7 @@
       <c r="F11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="3">
         <v>284.4772</v>
       </c>
       <c r="H11" s="2"/>
@@ -3288,9 +2901,13 @@
       <c r="J11" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2">
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -3308,7 +2925,7 @@
       <c r="F12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="3">
         <v>214.34</v>
       </c>
       <c r="H12" s="2"/>
@@ -3318,9 +2935,13 @@
       <c r="J12" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2">
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -3338,7 +2959,7 @@
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="3">
         <v>340.5836</v>
       </c>
       <c r="H13" s="2"/>
@@ -3348,9 +2969,13 @@
       <c r="J13" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2">
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -3368,7 +2993,7 @@
       <c r="F14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="3">
         <v>186.291</v>
       </c>
       <c r="H14" s="2"/>
@@ -3378,9 +3003,13 @@
       <c r="J14" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2">
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -3398,7 +3027,7 @@
       <c r="F15" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <v>304.4669</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -3410,9 +3039,13 @@
       <c r="J15" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2">
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -3430,7 +3063,7 @@
       <c r="F16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="3">
         <v>354.61</v>
       </c>
       <c r="H16" s="2"/>
@@ -3438,9 +3071,13 @@
         <v>112</v>
       </c>
       <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2">
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -3458,7 +3095,7 @@
       <c r="F17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="3">
         <v>278.4296</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -3470,9 +3107,13 @@
       <c r="J17" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2">
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -3490,7 +3131,7 @@
       <c r="F18" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="3">
         <v>330.5</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -3500,9 +3141,13 @@
         <v>126</v>
       </c>
       <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2">
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -3520,7 +3165,7 @@
       <c r="F19" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="3">
         <v>302.451</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -3532,9 +3177,13 @@
       <c r="J19" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2">
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -3552,7 +3201,7 @@
       <c r="F20" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="3">
         <v>226.355</v>
       </c>
       <c r="H20" s="2" t="s">
@@ -3564,9 +3213,13 @@
       <c r="J20" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2">
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -3584,7 +3237,7 @@
       <c r="F21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="3">
         <v>368.6367</v>
       </c>
       <c r="H21" s="2"/>
@@ -3594,9 +3247,13 @@
       <c r="J21" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2">
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -3614,7 +3271,7 @@
       <c r="F22" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="3">
         <v>338.5677</v>
       </c>
       <c r="H22" s="2" t="s">
@@ -3626,9 +3283,13 @@
       <c r="J22" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2">
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -3646,7 +3307,7 @@
       <c r="F23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="3">
         <v>282.4614</v>
       </c>
       <c r="H23" s="2"/>
@@ -3656,9 +3317,13 @@
       <c r="J23" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2">
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -3676,7 +3341,7 @@
       <c r="F24" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="3">
         <v>328.4883</v>
       </c>
       <c r="H24" s="2" t="s">
@@ -3688,9 +3353,13 @@
       <c r="J24" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2">
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -3708,7 +3377,7 @@
       <c r="F25" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="3">
         <v>312.5304</v>
       </c>
       <c r="H25" s="2"/>
@@ -3718,9 +3387,13 @@
       <c r="J25" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2">
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -3738,7 +3411,7 @@
       <c r="F26" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="3">
         <v>332.52</v>
       </c>
       <c r="H26" s="2" t="s">
@@ -3750,9 +3423,13 @@
       <c r="J26" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2">
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -3770,7 +3447,7 @@
       <c r="F27" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="3">
         <v>310.5145</v>
       </c>
       <c r="H27" s="2" t="s">
@@ -3782,9 +3459,13 @@
       <c r="J27" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2">
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -3802,7 +3483,7 @@
       <c r="F28" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="3">
         <v>270.45</v>
       </c>
       <c r="H28" s="2"/>
@@ -3810,9 +3491,13 @@
         <v>194</v>
       </c>
       <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2">
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -3830,7 +3515,7 @@
       <c r="F29" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="3">
         <v>326.56</v>
       </c>
       <c r="H29" s="2"/>
@@ -3838,9 +3523,13 @@
         <v>200</v>
       </c>
       <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2">
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -3858,7 +3547,7 @@
       <c r="F30" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="3">
         <v>366.6208</v>
       </c>
       <c r="H30" s="2" t="s">
@@ -3870,9 +3559,13 @@
       <c r="J30" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2">
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -3890,7 +3583,7 @@
       <c r="F31" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="3">
         <v>306.4828</v>
       </c>
       <c r="H31" s="2" t="s">
@@ -3902,9 +3595,13 @@
       <c r="J31" s="2" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="2">
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -3922,7 +3619,7 @@
       <c r="F32" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="3">
         <v>278.4296</v>
       </c>
       <c r="H32" s="2" t="s">
@@ -3934,9 +3631,13 @@
       <c r="J32" s="2" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="2">
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -3954,7 +3655,7 @@
       <c r="F33" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="3">
         <v>254.4082</v>
       </c>
       <c r="H33" s="2" t="s">
@@ -3966,9 +3667,13 @@
       <c r="J33" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="2">
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -3986,7 +3691,7 @@
       <c r="F34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="3">
         <v>282.4614</v>
       </c>
       <c r="H34" s="2"/>
@@ -3996,9 +3701,13 @@
       <c r="J34" s="2" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="2">
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -4016,7 +3725,7 @@
       <c r="F35" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35" s="3">
         <v>308.4986</v>
       </c>
       <c r="H35" s="2" t="s">
@@ -4028,9 +3737,13 @@
       <c r="J35" s="2" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="2">
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -4048,7 +3761,7 @@
       <c r="F36" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="3">
         <v>280.4455</v>
       </c>
       <c r="H36" s="2"/>
@@ -4056,9 +3769,13 @@
         <v>245</v>
       </c>
       <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="2">
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -4076,7 +3793,7 @@
       <c r="F37" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="3">
         <v>330.5042</v>
       </c>
       <c r="H37" s="2" t="s">
@@ -4088,9 +3805,13 @@
       <c r="J37" s="2" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="2">
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -4108,7 +3829,7 @@
       <c r="F38" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="3">
         <v>254.4082</v>
       </c>
       <c r="H38" s="2"/>
@@ -4116,9 +3837,13 @@
         <v>255</v>
       </c>
       <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="2">
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -4136,7 +3861,7 @@
       <c r="F39" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="3">
         <v>268.4348</v>
       </c>
       <c r="H39" s="2"/>
@@ -4144,9 +3869,13 @@
         <v>261</v>
       </c>
       <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="2">
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -4164,7 +3893,7 @@
       <c r="F40" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="3">
         <v>306.4828</v>
       </c>
       <c r="H40" s="2" t="s">
@@ -4176,9 +3905,13 @@
       <c r="J40" s="2" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="2">
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -4196,7 +3929,7 @@
       <c r="F41" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41" s="3">
         <v>336.5518</v>
       </c>
       <c r="H41" s="2" t="s">
@@ -4208,9 +3941,13 @@
       <c r="J41" s="2" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="2">
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -4228,7 +3965,7 @@
       <c r="F42" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42" s="3">
         <v>226.36</v>
       </c>
       <c r="H42" s="2"/>
@@ -4236,9 +3973,13 @@
         <v>278</v>
       </c>
       <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="2">
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -4256,7 +3997,7 @@
       <c r="F43" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43" s="3">
         <v>282.46</v>
       </c>
       <c r="H43" s="2" t="s">
@@ -4268,9 +4009,13 @@
       <c r="J43" s="2" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="2">
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -4288,7 +4033,7 @@
       <c r="F44" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44" s="3">
         <v>268.4348</v>
       </c>
       <c r="H44" s="2"/>
@@ -4296,9 +4041,13 @@
         <v>287</v>
       </c>
       <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="2">
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -4316,7 +4065,7 @@
       <c r="F45" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="3">
         <v>338.57</v>
       </c>
       <c r="H45" s="2"/>
@@ -4324,9 +4073,13 @@
         <v>291</v>
       </c>
       <c r="J45" s="2"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="2">
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -4344,7 +4097,7 @@
       <c r="F46" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G46" s="2">
+      <c r="G46" s="3">
         <v>282.46</v>
       </c>
       <c r="H46" s="2"/>
@@ -4352,9 +4105,13 @@
         <v>295</v>
       </c>
       <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="2">
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -4372,7 +4129,7 @@
       <c r="F47" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G47" s="3">
         <v>240.38</v>
       </c>
       <c r="H47" s="2"/>
@@ -4380,9 +4137,13 @@
         <v>301</v>
       </c>
       <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="2">
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -4400,15 +4161,19 @@
       <c r="F48" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G48" s="3">
         <v>240.38</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="2">
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -4426,15 +4191,19 @@
       <c r="F49" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="3">
         <v>296.5</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="2">
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -4452,15 +4221,18 @@
       <c r="F50" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="3">
         <v>310.51</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="6"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>